--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9148,0.0414,0.0210,0.0046</t>
-  </si>
-  <si>
-    <t>0.9676,0.0065,0.0098,0.0045</t>
-  </si>
-  <si>
-    <t>0.9806,0.0047,0.0028,0.0022</t>
-  </si>
-  <si>
-    <t>0.9678,0.0139,0.0036,0.0031</t>
-  </si>
-  <si>
-    <t>0.8910,0.0535,0.0052,0.0147</t>
-  </si>
-  <si>
-    <t>0.9043,0.0656,0.0057,0.0042</t>
-  </si>
-  <si>
-    <t>0.7471,0.2106,0.0230,0.0089</t>
-  </si>
-  <si>
-    <t>0.9365,0.0418,0.0053,0.0041</t>
-  </si>
-  <si>
-    <t>0.9330,0.0442,0.0037,0.0026</t>
-  </si>
-  <si>
-    <t>0.7862,0.1974,0.0062,0.0041</t>
-  </si>
-  <si>
-    <t>0.8934,0.0578,0.0100,0.0118</t>
-  </si>
-  <si>
-    <t>0.9732,0.0135,0.0032,0.0029</t>
-  </si>
-  <si>
-    <t>0.9742,0.0074,0.0093,0.0016</t>
-  </si>
-  <si>
-    <t>0.9590,0.0155,0.0227,0.0009</t>
-  </si>
-  <si>
-    <t>0.9938,0.0019,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.9883,0.0016,0.0089,0.0002</t>
-  </si>
-  <si>
-    <t>0.9794,0.0062,0.0053,0.0004</t>
-  </si>
-  <si>
-    <t>0.8357,0.2322,0.0036,0.0003</t>
-  </si>
-  <si>
-    <t>0.8833,0.1285,0.0075,0.0014</t>
-  </si>
-  <si>
-    <t>0.5060,0.5416,0.0199,0.0032</t>
-  </si>
-  <si>
-    <t>0.3756,0.7640,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.6210,0.4903,0.0036,0.0003</t>
-  </si>
-  <si>
-    <t>0.9126,0.0379,0.0461,0.0010</t>
-  </si>
-  <si>
-    <t>0.9535,0.0090,0.0390,0.0005</t>
-  </si>
-  <si>
-    <t>0.9051,0.0171,0.1100,0.0009</t>
-  </si>
-  <si>
-    <t>0.9612,0.0105,0.0308,0.0008</t>
-  </si>
-  <si>
-    <t>0.9904,0.0016,0.0073,0.0001</t>
-  </si>
-  <si>
-    <t>0.9550,0.0148,0.0194,0.0010</t>
-  </si>
-  <si>
-    <t>0.9743,0.0019,0.0527,0.0002</t>
-  </si>
-  <si>
-    <t>0.9070,0.1515,0.0033,0.0001</t>
-  </si>
-  <si>
-    <t>0.9554,0.0430,0.0021,0.0006</t>
-  </si>
-  <si>
-    <t>0.0343,0.6497,0.8882,0.0039</t>
-  </si>
-  <si>
-    <t>0.7082,0.3652,0.0059,0.0010</t>
-  </si>
-  <si>
-    <t>0.9478,0.0324,0.0024,0.0011</t>
-  </si>
-  <si>
-    <t>0.9187,0.0708,0.0163,0.0011</t>
-  </si>
-  <si>
-    <t>0.9340,0.0674,0.0017,0.0009</t>
-  </si>
-  <si>
-    <t>0.9792,0.0163,0.0022,0.0002</t>
-  </si>
-  <si>
-    <t>0.6994,0.1399,0.1801,0.0038</t>
-  </si>
-  <si>
-    <t>0.9804,0.0016,0.0266,0.0008</t>
-  </si>
-  <si>
-    <t>0.5373,0.2149,0.2938,0.0022</t>
-  </si>
-  <si>
-    <t>0.9397,0.0183,0.0194,0.0065</t>
-  </si>
-  <si>
-    <t>0.8967,0.0398,0.0528,0.0009</t>
-  </si>
-  <si>
-    <t>0.8638,0.0972,0.0315,0.0007</t>
-  </si>
-  <si>
-    <t>0.9166,0.0291,0.0512,0.0007</t>
-  </si>
-  <si>
-    <t>0.8700,0.1450,0.0056,0.0008</t>
-  </si>
-  <si>
-    <t>0.1607,0.9008,0.0069,0.0003</t>
-  </si>
-  <si>
-    <t>0.7231,0.3387,0.0124,0.0003</t>
-  </si>
-  <si>
-    <t>0.3553,0.7863,0.0074,0.0004</t>
-  </si>
-  <si>
-    <t>0.9545,0.0082,0.0663,0.0008</t>
-  </si>
-  <si>
-    <t>0.3544,0.2694,0.5514,0.0018</t>
-  </si>
-  <si>
-    <t>0.9770,0.0086,0.0119,0.0003</t>
-  </si>
-  <si>
-    <t>0.9754,0.0053,0.0222,0.0002</t>
-  </si>
-  <si>
-    <t>0.4784,0.1917,0.2551,0.0012</t>
-  </si>
-  <si>
-    <t>0.7338,0.0447,0.3172,0.0016</t>
-  </si>
-  <si>
-    <t>0.9215,0.0842,0.0026,0.0013</t>
-  </si>
-  <si>
-    <t>0.7675,0.1819,0.0170,0.0073</t>
-  </si>
-  <si>
-    <t>0.9401,0.0466,0.0025,0.0034</t>
-  </si>
-  <si>
-    <t>0.7233,0.2293,0.1066,0.0070</t>
-  </si>
-  <si>
-    <t>0.9376,0.0456,0.0097,0.0043</t>
-  </si>
-  <si>
-    <t>0.8586,0.1131,0.0332,0.0066</t>
-  </si>
-  <si>
-    <t>0.9085,0.0577,0.0076,0.0086</t>
-  </si>
-  <si>
-    <t>0.0293,0.8666,0.7452,0.0013</t>
-  </si>
-  <si>
-    <t>0.6156,0.0554,0.5033,0.0006</t>
-  </si>
-  <si>
-    <t>0.9190,0.0120,0.1289,0.0008</t>
-  </si>
-  <si>
-    <t>0.0156,0.9094,0.8079,0.0004</t>
-  </si>
-  <si>
-    <t>0.0133,0.6895,0.9563,0.0007</t>
-  </si>
-  <si>
-    <t>0.8791,0.1930,0.0043,0.0002</t>
-  </si>
-  <si>
-    <t>0.2713,0.8658,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.9554,0.0575,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9472,0.0484,0.0036,0.0006</t>
-  </si>
-  <si>
-    <t>0.8823,0.1479,0.0103,0.0006</t>
-  </si>
-  <si>
-    <t>0.1127,0.7636,0.3581,0.0007</t>
-  </si>
-  <si>
-    <t>0.6839,0.3010,0.0379,0.0001</t>
-  </si>
-  <si>
-    <t>0.3038,0.7212,0.0774,0.0007</t>
-  </si>
-  <si>
-    <t>0.0059,0.9555,0.8393,0.0003</t>
-  </si>
-  <si>
-    <t>0.9835,0.0021,0.0165,0.0005</t>
-  </si>
-  <si>
-    <t>0.9306,0.0191,0.0116,0.0099</t>
-  </si>
-  <si>
-    <t>0.9432,0.0121,0.0197,0.0099</t>
-  </si>
-  <si>
-    <t>0.9865,0.0024,0.0059,0.0014</t>
-  </si>
-  <si>
-    <t>0.9776,0.0033,0.0170,0.0018</t>
-  </si>
-  <si>
-    <t>0.9428,0.0134,0.0081,0.0047</t>
-  </si>
-  <si>
-    <t>0.0196,0.9352,0.6896,0.0015</t>
-  </si>
-  <si>
-    <t>0.1787,0.5189,0.5554,0.0012</t>
-  </si>
-  <si>
-    <t>0.7814,0.0779,0.1989,0.0024</t>
-  </si>
-  <si>
-    <t>0.2299,0.5106,0.3737,0.0007</t>
-  </si>
-  <si>
-    <t>0.1579,0.8112,0.1356,0.0006</t>
-  </si>
-  <si>
-    <t>0.2044,0.7101,0.2542,0.0014</t>
-  </si>
-  <si>
-    <t>0.8743,0.0996,0.0066,0.0040</t>
-  </si>
-  <si>
-    <t>0.8451,0.0789,0.0045,0.0123</t>
-  </si>
-  <si>
-    <t>0.6917,0.2645,0.0137,0.0055</t>
-  </si>
-  <si>
-    <t>0.8465,0.0928,0.0064,0.0169</t>
-  </si>
-  <si>
-    <t>0.8352,0.1167,0.0152,0.0075</t>
-  </si>
-  <si>
-    <t>0.6141,0.3658,0.0142,0.0072</t>
-  </si>
-  <si>
-    <t>0.9732,0.0213,0.0019,0.0011</t>
-  </si>
-  <si>
-    <t>0.8998,0.0963,0.0093,0.0023</t>
-  </si>
-  <si>
-    <t>0.4728,0.2819,0.0094,0.0300</t>
-  </si>
-  <si>
-    <t>0.9642,0.0268,0.0026,0.0013</t>
-  </si>
-  <si>
-    <t>0.8278,0.1536,0.0109,0.0073</t>
-  </si>
-  <si>
-    <t>0.8858,0.0741,0.0122,0.0114</t>
-  </si>
-  <si>
-    <t>0.8605,0.0934,0.0042,0.0054</t>
-  </si>
-  <si>
-    <t>0.9303,0.0624,0.0033,0.0011</t>
-  </si>
-  <si>
-    <t>0.9194,0.0632,0.0046,0.0024</t>
-  </si>
-  <si>
-    <t>0.9307,0.0328,0.0059,0.0084</t>
-  </si>
-  <si>
-    <t>0.6249,0.0469,0.4739,0.0008</t>
-  </si>
-  <si>
-    <t>0.9376,0.0254,0.0207,0.0016</t>
-  </si>
-  <si>
-    <t>0.9649,0.0150,0.0144,0.0005</t>
-  </si>
-  <si>
-    <t>0.9810,0.0046,0.0142,0.0003</t>
-  </si>
-  <si>
-    <t>0.1250,0.9055,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.0449,0.9683,0.0036,0.0011</t>
-  </si>
-  <si>
-    <t>0.9013,0.1107,0.0040,0.0012</t>
-  </si>
-  <si>
-    <t>0.8917,0.1624,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.4508,0.6483,0.0008,0.0012</t>
-  </si>
-  <si>
-    <t>0.0167,0.9796,0.0074,0.0033</t>
-  </si>
-  <si>
-    <t>0.8536,0.1570,0.0126,0.0022</t>
-  </si>
-  <si>
-    <t>0.9355,0.0665,0.0042,0.0003</t>
-  </si>
-  <si>
-    <t>0.9407,0.0437,0.0098,0.0003</t>
-  </si>
-  <si>
-    <t>0.9749,0.0086,0.0076,0.0003</t>
-  </si>
-  <si>
-    <t>0.9280,0.0531,0.0122,0.0007</t>
-  </si>
-  <si>
-    <t>0.9795,0.0115,0.0028,0.0006</t>
-  </si>
-  <si>
-    <t>0.7598,0.3313,0.0069,0.0005</t>
-  </si>
-  <si>
-    <t>0.8157,0.2780,0.0052,0.0002</t>
-  </si>
-  <si>
-    <t>0.1977,0.8734,0.0026,0.0003</t>
-  </si>
-  <si>
-    <t>0.2110,0.8060,0.0625,0.0017</t>
-  </si>
-  <si>
-    <t>0.8947,0.1180,0.0029,0.0006</t>
-  </si>
-  <si>
-    <t>0.8689,0.1453,0.0055,0.0008</t>
-  </si>
-  <si>
-    <t>0.8198,0.2256,0.0050,0.0016</t>
-  </si>
-  <si>
-    <t>0.9684,0.0191,0.0021,0.0025</t>
-  </si>
-  <si>
-    <t>0.9459,0.0313,0.0039,0.0040</t>
-  </si>
-  <si>
-    <t>0.9573,0.0182,0.0043,0.0047</t>
-  </si>
-  <si>
-    <t>0.8357,0.0752,0.0064,0.0218</t>
-  </si>
-  <si>
-    <t>0.9539,0.0346,0.0028,0.0022</t>
-  </si>
-  <si>
-    <t>0.9090,0.0933,0.0055,0.0010</t>
-  </si>
-  <si>
-    <t>0.8610,0.0896,0.0052,0.0076</t>
-  </si>
-  <si>
-    <t>0.8926,0.1022,0.0041,0.0015</t>
-  </si>
-  <si>
-    <t>0.8246,0.0678,0.1064,0.0014</t>
-  </si>
-  <si>
-    <t>0.8482,0.0780,0.0741,0.0017</t>
-  </si>
-  <si>
-    <t>0.4557,0.2545,0.2951,0.0018</t>
-  </si>
-  <si>
-    <t>0.9282,0.0298,0.0313,0.0007</t>
-  </si>
-  <si>
-    <t>0.9916,0.0011,0.0077,0.0002</t>
-  </si>
-  <si>
-    <t>0.9658,0.0116,0.0068,0.0011</t>
-  </si>
-  <si>
-    <t>0.9874,0.0044,0.0042,0.0002</t>
-  </si>
-  <si>
-    <t>0.9888,0.0044,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.9745,0.0077,0.0092,0.0027</t>
-  </si>
-  <si>
-    <t>0.9575,0.0036,0.0075,0.0186</t>
-  </si>
-  <si>
-    <t>0.9591,0.0055,0.0097,0.0108</t>
-  </si>
-  <si>
-    <t>0.9104,0.0186,0.0328,0.0136</t>
-  </si>
-  <si>
-    <t>0.2774,0.5519,0.3438,0.0052</t>
-  </si>
-  <si>
-    <t>0.8532,0.1111,0.0064,0.0059</t>
-  </si>
-  <si>
-    <t>0.3506,0.7492,0.0047,0.0008</t>
-  </si>
-  <si>
-    <t>0.8818,0.0851,0.0079,0.0072</t>
-  </si>
-  <si>
-    <t>0.7785,0.2678,0.0126,0.0014</t>
-  </si>
-  <si>
-    <t>0.9494,0.0331,0.0043,0.0023</t>
-  </si>
-  <si>
-    <t>0.9018,0.0686,0.0022,0.0020</t>
-  </si>
-  <si>
-    <t>0.9038,0.0771,0.0062,0.0027</t>
-  </si>
-  <si>
-    <t>0.4899,0.2439,0.4329,0.0323</t>
-  </si>
-  <si>
-    <t>0.9890,0.0038,0.0019,0.0005</t>
-  </si>
-  <si>
-    <t>0.8059,0.1383,0.0050,0.0044</t>
-  </si>
-  <si>
-    <t>0.5162,0.5430,0.0094,0.0011</t>
-  </si>
-  <si>
-    <t>0.9447,0.0546,0.0050,0.0004</t>
-  </si>
-  <si>
-    <t>0.9601,0.0356,0.0030,0.0005</t>
-  </si>
-  <si>
-    <t>0.7574,0.3395,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.9862,0.0082,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.9789,0.0210,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.5508,0.3930,0.0085,0.0089</t>
-  </si>
-  <si>
-    <t>0.8805,0.0490,0.0077,0.0189</t>
-  </si>
-  <si>
-    <t>0.8060,0.2292,0.0101,0.0019</t>
-  </si>
-  <si>
-    <t>0.8485,0.0641,0.0096,0.0213</t>
-  </si>
-  <si>
-    <t>0.9198,0.0554,0.0099,0.0054</t>
-  </si>
-  <si>
-    <t>0.9514,0.0256,0.0036,0.0039</t>
-  </si>
-  <si>
-    <t>0.8652,0.0739,0.0064,0.0132</t>
-  </si>
-  <si>
-    <t>0.8888,0.0741,0.0056,0.0088</t>
-  </si>
-  <si>
-    <t>0.7890,0.1903,0.0106,0.0059</t>
-  </si>
-  <si>
-    <t>0.8274,0.1780,0.0048,0.0018</t>
-  </si>
-  <si>
-    <t>0.1797,0.8067,0.0117,0.0268</t>
-  </si>
-  <si>
-    <t>0.9541,0.0348,0.0017,0.0007</t>
-  </si>
-  <si>
-    <t>0.8827,0.0968,0.0026,0.0016</t>
-  </si>
-  <si>
-    <t>0.9394,0.0320,0.0013,0.0036</t>
-  </si>
-  <si>
-    <t>0.9605,0.0288,0.0024,0.0019</t>
-  </si>
-  <si>
-    <t>0.7962,0.2211,0.0045,0.0027</t>
-  </si>
-  <si>
-    <t>0.1541,0.4736,0.6282,0.0066</t>
-  </si>
-  <si>
-    <t>0.8604,0.1643,0.0029,0.0009</t>
-  </si>
-  <si>
-    <t>0.1561,0.1358,0.7863,0.0013</t>
-  </si>
-  <si>
-    <t>0.8088,0.0662,0.0929,0.0009</t>
-  </si>
-  <si>
-    <t>0.8662,0.0774,0.0473,0.0015</t>
-  </si>
-  <si>
-    <t>0.3232,0.0391,0.8412,0.0001</t>
-  </si>
-  <si>
-    <t>0.8732,0.0697,0.0393,0.0005</t>
-  </si>
-  <si>
-    <t>0.9854,0.0019,0.0181,0.0001</t>
-  </si>
-  <si>
-    <t>0.7713,0.0551,0.1794,0.0010</t>
-  </si>
-  <si>
-    <t>0.9096,0.0818,0.0103,0.0005</t>
-  </si>
-  <si>
-    <t>0.9847,0.0036,0.0063,0.0004</t>
-  </si>
-  <si>
-    <t>0.9347,0.0408,0.0130,0.0011</t>
-  </si>
-  <si>
-    <t>0.9907,0.0053,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.3225,0.7689,0.0088,0.0005</t>
-  </si>
-  <si>
-    <t>0.9819,0.0048,0.0066,0.0006</t>
-  </si>
-  <si>
-    <t>0.9703,0.0167,0.0040,0.0006</t>
-  </si>
-  <si>
-    <t>0.8849,0.0706,0.0277,0.0038</t>
-  </si>
-  <si>
-    <t>0.8980,0.1182,0.0028,0.0007</t>
-  </si>
-  <si>
-    <t>0.9494,0.0485,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.9170,0.0792,0.0062,0.0009</t>
-  </si>
-  <si>
-    <t>0.6922,0.3016,0.0045,0.0043</t>
-  </si>
-  <si>
-    <t>0.7967,0.2190,0.0044,0.0026</t>
-  </si>
-  <si>
-    <t>0.9880,0.0021,0.0058,0.0004</t>
-  </si>
-  <si>
-    <t>0.9390,0.0210,0.0292,0.0022</t>
-  </si>
-  <si>
-    <t>0.9627,0.0074,0.0171,0.0020</t>
-  </si>
-  <si>
-    <t>0.9789,0.0029,0.0281,0.0004</t>
-  </si>
-  <si>
-    <t>0.9051,0.0498,0.0171,0.0069</t>
-  </si>
-  <si>
-    <t>0.9184,0.0187,0.0709,0.0008</t>
-  </si>
-  <si>
-    <t>0.9512,0.0191,0.0232,0.0008</t>
-  </si>
-  <si>
-    <t>0.9447,0.0232,0.0241,0.0010</t>
-  </si>
-  <si>
-    <t>0.8121,0.0427,0.1591,0.0025</t>
-  </si>
-  <si>
-    <t>0.7160,0.1369,0.1239,0.0016</t>
-  </si>
-  <si>
-    <t>0.9555,0.0312,0.0022,0.0022</t>
-  </si>
-  <si>
-    <t>0.8930,0.0634,0.0134,0.0101</t>
-  </si>
-  <si>
-    <t>0.9379,0.0464,0.0050,0.0035</t>
-  </si>
-  <si>
-    <t>0.9204,0.0590,0.0115,0.0057</t>
-  </si>
-  <si>
-    <t>0.8514,0.1418,0.0026,0.0035</t>
-  </si>
-  <si>
-    <t>0.8157,0.1540,0.0028,0.0027</t>
-  </si>
-  <si>
-    <t>0.7455,0.1791,0.0141,0.0133</t>
-  </si>
-  <si>
-    <t>0.7701,0.2106,0.0031,0.0026</t>
-  </si>
-  <si>
-    <t>0.7903,0.2423,0.0175,0.0009</t>
-  </si>
-  <si>
-    <t>0.9530,0.0459,0.0039,0.0004</t>
-  </si>
-  <si>
-    <t>0.9272,0.0743,0.0069,0.0006</t>
-  </si>
-  <si>
-    <t>0.7729,0.0319,0.2830,0.0004</t>
-  </si>
-  <si>
-    <t>0.7893,0.0501,0.2536,0.0030</t>
-  </si>
-  <si>
-    <t>0.9212,0.0446,0.0245,0.0006</t>
-  </si>
-  <si>
-    <t>0.2839,0.1263,0.7232,0.0009</t>
-  </si>
-  <si>
-    <t>0.8865,0.0463,0.0475,0.0018</t>
-  </si>
-  <si>
-    <t>0.0753,0.0622,0.9596,0.0004</t>
-  </si>
-  <si>
-    <t>0.9400,0.0124,0.0575,0.0009</t>
-  </si>
-  <si>
-    <t>0.9625,0.0170,0.0061,0.0010</t>
-  </si>
-  <si>
-    <t>0.9907,0.0028,0.0052,0.0001</t>
-  </si>
-  <si>
-    <t>0.9913,0.0020,0.0049,0.0003</t>
-  </si>
-  <si>
-    <t>0.9869,0.0036,0.0020,0.0007</t>
-  </si>
-  <si>
-    <t>0.8615,0.0786,0.0121,0.0095</t>
-  </si>
-  <si>
-    <t>0.8624,0.1124,0.0048,0.0040</t>
-  </si>
-  <si>
-    <t>0.9399,0.0478,0.0024,0.0016</t>
-  </si>
-  <si>
-    <t>0.6406,0.3294,0.0085,0.0078</t>
-  </si>
-  <si>
-    <t>0.8879,0.0730,0.0048,0.0088</t>
-  </si>
-  <si>
-    <t>0.8187,0.1554,0.0106,0.0065</t>
-  </si>
-  <si>
-    <t>0.9551,0.0278,0.0013,0.0023</t>
-  </si>
-  <si>
-    <t>0.6550,0.2901,0.0082,0.0124</t>
-  </si>
-  <si>
-    <t>0.8648,0.0536,0.0518,0.0006</t>
-  </si>
-  <si>
-    <t>0.8002,0.0334,0.1960,0.0006</t>
-  </si>
-  <si>
-    <t>0.2452,0.3161,0.6176,0.0042</t>
-  </si>
-  <si>
-    <t>0.9776,0.0069,0.0107,0.0004</t>
-  </si>
-  <si>
-    <t>0.9357,0.0043,0.1147,0.0017</t>
-  </si>
-  <si>
-    <t>0.9713,0.0063,0.0138,0.0024</t>
-  </si>
-  <si>
-    <t>0.9815,0.0037,0.0121,0.0005</t>
-  </si>
-  <si>
-    <t>0.9696,0.0051,0.0212,0.0021</t>
-  </si>
-  <si>
-    <t>0.9709,0.0140,0.0077,0.0020</t>
-  </si>
-  <si>
-    <t>0.9656,0.0052,0.0170,0.0051</t>
-  </si>
-  <si>
-    <t>0.9641,0.0048,0.0234,0.0054</t>
-  </si>
-  <si>
-    <t>0.9548,0.0042,0.0341,0.0047</t>
-  </si>
-  <si>
-    <t>0.8789,0.0130,0.0188,0.0642</t>
-  </si>
-  <si>
-    <t>0.9497,0.0302,0.0072,0.0017</t>
+    <t>0.8435,0.0511,0.0011,0.0727</t>
+  </si>
+  <si>
+    <t>0.0309,0.0029,0.0086,0.9779</t>
+  </si>
+  <si>
+    <t>0.7591,0.0074,0.0059,0.2848</t>
+  </si>
+  <si>
+    <t>0.0241,0.0023,0.0012,0.9871</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0010,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9840,0.0178,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9982,0.0009,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9980,0.0005,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9969,0.0024,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9658,0.0070,0.0264,0.0017</t>
+  </si>
+  <si>
+    <t>0.3626,0.0310,0.6565,0.0044</t>
+  </si>
+  <si>
+    <t>0.7943,0.0077,0.3236,0.0006</t>
+  </si>
+  <si>
+    <t>0.0265,0.0061,0.9652,0.0012</t>
+  </si>
+  <si>
+    <t>0.8665,0.0123,0.1784,0.0015</t>
+  </si>
+  <si>
+    <t>0.0023,0.9956,0.0010,0.0026</t>
+  </si>
+  <si>
+    <t>0.0433,0.9588,0.0042,0.0009</t>
+  </si>
+  <si>
+    <t>0.0262,0.9803,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.0365,0.9751,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.0015,0.9974,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.7603,0.0027,0.3841,0.0049</t>
+  </si>
+  <si>
+    <t>0.4079,0.0274,0.6612,0.0087</t>
+  </si>
+  <si>
+    <t>0.0184,0.0150,0.9647,0.0121</t>
+  </si>
+  <si>
+    <t>0.0348,0.0073,0.9547,0.0008</t>
+  </si>
+  <si>
+    <t>0.0830,0.0299,0.9266,0.0052</t>
+  </si>
+  <si>
+    <t>0.0632,0.0215,0.9081,0.0313</t>
+  </si>
+  <si>
+    <t>0.0103,0.0031,0.9864,0.0017</t>
+  </si>
+  <si>
+    <t>0.1650,0.8639,0.0194,0.0019</t>
+  </si>
+  <si>
+    <t>0.6908,0.1245,0.2543,0.0150</t>
+  </si>
+  <si>
+    <t>0.0016,0.0173,0.9900,0.0090</t>
+  </si>
+  <si>
+    <t>0.0207,0.9532,0.0421,0.0009</t>
+  </si>
+  <si>
+    <t>0.8738,0.1139,0.0222,0.0183</t>
+  </si>
+  <si>
+    <t>0.8610,0.0566,0.0509,0.0097</t>
+  </si>
+  <si>
+    <t>0.6470,0.4626,0.0085,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.9934,0.3234,0.0001</t>
+  </si>
+  <si>
+    <t>0.0280,0.8342,0.2058,0.0075</t>
+  </si>
+  <si>
+    <t>0.2756,0.0252,0.5982,0.0918</t>
+  </si>
+  <si>
+    <t>0.3373,0.0205,0.7844,0.0034</t>
+  </si>
+  <si>
+    <t>0.5897,0.0055,0.3587,0.0507</t>
+  </si>
+  <si>
+    <t>0.0454,0.0404,0.9481,0.0007</t>
+  </si>
+  <si>
+    <t>0.0147,0.9682,0.0070,0.0031</t>
+  </si>
+  <si>
+    <t>0.0047,0.0119,0.9865,0.0005</t>
+  </si>
+  <si>
+    <t>0.0789,0.8391,0.0151,0.3896</t>
+  </si>
+  <si>
+    <t>0.0049,0.9878,0.0062,0.0085</t>
+  </si>
+  <si>
+    <t>0.0019,0.9929,0.0045,0.0009</t>
+  </si>
+  <si>
+    <t>0.0022,0.9952,0.0155,0.0002</t>
+  </si>
+  <si>
+    <t>0.0539,0.0045,0.9710,0.0015</t>
+  </si>
+  <si>
+    <t>0.0076,0.0192,0.9855,0.0027</t>
+  </si>
+  <si>
+    <t>0.0141,0.0041,0.9774,0.0029</t>
+  </si>
+  <si>
+    <t>0.0098,0.0077,0.9743,0.0088</t>
+  </si>
+  <si>
+    <t>0.0061,0.0398,0.9904,0.0009</t>
+  </si>
+  <si>
+    <t>0.0093,0.0104,0.9888,0.0005</t>
+  </si>
+  <si>
+    <t>0.8713,0.2377,0.0026,0.0003</t>
+  </si>
+  <si>
+    <t>0.9863,0.0051,0.0060,0.0029</t>
+  </si>
+  <si>
+    <t>0.9641,0.0502,0.0035,0.0022</t>
+  </si>
+  <si>
+    <t>0.0045,0.0360,0.9843,0.0099</t>
+  </si>
+  <si>
+    <t>0.9905,0.0054,0.0035,0.0013</t>
+  </si>
+  <si>
+    <t>0.9988,0.0012,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9824,0.0242,0.0031,0.0006</t>
+  </si>
+  <si>
+    <t>0.0008,0.8240,0.9876,0.0002</t>
+  </si>
+  <si>
+    <t>0.0589,0.0303,0.9732,0.0003</t>
+  </si>
+  <si>
+    <t>0.0247,0.0172,0.9623,0.0043</t>
+  </si>
+  <si>
+    <t>0.0002,0.9784,0.9515,0.0001</t>
+  </si>
+  <si>
+    <t>0.0122,0.0074,0.9834,0.0023</t>
+  </si>
+  <si>
+    <t>0.5358,0.5495,0.0078,0.0028</t>
+  </si>
+  <si>
+    <t>0.0058,0.9967,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8405,0.0773,0.1599,0.0089</t>
+  </si>
+  <si>
+    <t>0.8914,0.1171,0.0232,0.0021</t>
+  </si>
+  <si>
+    <t>0.0098,0.0349,0.9825,0.0012</t>
+  </si>
+  <si>
+    <t>0.0014,0.8896,0.8563,0.0002</t>
+  </si>
+  <si>
+    <t>0.0037,0.7612,0.9129,0.0006</t>
+  </si>
+  <si>
+    <t>0.0054,0.9837,0.0620,0.0008</t>
+  </si>
+  <si>
+    <t>0.0033,0.9641,0.4430,0.0009</t>
+  </si>
+  <si>
+    <t>0.0199,0.0008,0.0350,0.9687</t>
+  </si>
+  <si>
+    <t>0.0040,0.0007,0.0018,0.9971</t>
+  </si>
+  <si>
+    <t>0.0118,0.0028,0.0020,0.9928</t>
+  </si>
+  <si>
+    <t>0.0978,0.0037,0.0105,0.9516</t>
+  </si>
+  <si>
+    <t>0.0008,0.0057,0.0016,0.9982</t>
+  </si>
+  <si>
+    <t>0.0150,0.0144,0.0030,0.9859</t>
+  </si>
+  <si>
+    <t>0.0001,0.9677,0.9918,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.8827,0.9723,0.0006</t>
+  </si>
+  <si>
+    <t>0.0213,0.5844,0.7475,0.0029</t>
+  </si>
+  <si>
+    <t>0.0005,0.6380,0.9843,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.7271,0.9832,0.0001</t>
+  </si>
+  <si>
+    <t>0.0047,0.6900,0.8751,0.0010</t>
+  </si>
+  <si>
+    <t>0.9954,0.0012,0.0005,0.0019</t>
+  </si>
+  <si>
+    <t>0.9988,0.0011,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9959,0.0042,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9943,0.0028,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9901,0.0097,0.0014,0.0010</t>
+  </si>
+  <si>
+    <t>0.9968,0.0023,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9968,0.0040,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9961,0.0033,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9966,0.0021,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9961,0.0016,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9972,0.0019,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0145,0.0051,0.9920,0.0003</t>
+  </si>
+  <si>
+    <t>0.0397,0.0776,0.9260,0.0021</t>
+  </si>
+  <si>
+    <t>0.7936,0.1278,0.0662,0.0428</t>
+  </si>
+  <si>
+    <t>0.0019,0.0029,0.9934,0.0010</t>
+  </si>
+  <si>
+    <t>0.3322,0.8094,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.0425,0.9705,0.0015,0.0011</t>
+  </si>
+  <si>
+    <t>0.0334,0.9756,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.0034,0.9937,0.0014,0.0031</t>
+  </si>
+  <si>
+    <t>0.1075,0.9216,0.0033,0.0024</t>
+  </si>
+  <si>
+    <t>0.0020,0.9971,0.0028,0.0002</t>
+  </si>
+  <si>
+    <t>0.9757,0.0452,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9235,0.0105,0.0927,0.0027</t>
+  </si>
+  <si>
+    <t>0.3711,0.0188,0.7175,0.0058</t>
+  </si>
+  <si>
+    <t>0.7697,0.0217,0.2365,0.0062</t>
+  </si>
+  <si>
+    <t>0.8177,0.0149,0.2089,0.0111</t>
+  </si>
+  <si>
+    <t>0.3158,0.0249,0.5953,0.1308</t>
+  </si>
+  <si>
+    <t>0.0043,0.9940,0.0028,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.9971,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.9957,0.0207,0.0061</t>
+  </si>
+  <si>
+    <t>0.0008,0.9270,0.9100,0.0003</t>
+  </si>
+  <si>
+    <t>0.0019,0.9976,0.0032,0.0000</t>
+  </si>
+  <si>
+    <t>0.6561,0.4338,0.0181,0.0011</t>
+  </si>
+  <si>
+    <t>0.9719,0.0389,0.0044,0.0002</t>
+  </si>
+  <si>
+    <t>0.9854,0.0170,0.0019,0.0010</t>
+  </si>
+  <si>
+    <t>0.9965,0.0013,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.9961,0.0007,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.9776,0.0185,0.0078,0.0021</t>
+  </si>
+  <si>
+    <t>0.9977,0.0012,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9961,0.0020,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.9899,0.0063,0.0023,0.0016</t>
+  </si>
+  <si>
+    <t>0.9939,0.0037,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.0050,0.3397,0.9628,0.0018</t>
+  </si>
+  <si>
+    <t>0.0015,0.8194,0.9657,0.0004</t>
+  </si>
+  <si>
+    <t>0.0116,0.2292,0.8543,0.0007</t>
+  </si>
+  <si>
+    <t>0.0403,0.0338,0.9628,0.0005</t>
+  </si>
+  <si>
+    <t>0.8865,0.1085,0.0097,0.0118</t>
+  </si>
+  <si>
+    <t>0.9647,0.0015,0.0455,0.0009</t>
+  </si>
+  <si>
+    <t>0.2714,0.0016,0.8731,0.0011</t>
+  </si>
+  <si>
+    <t>0.4668,0.0363,0.6237,0.0040</t>
+  </si>
+  <si>
+    <t>0.2308,0.0031,0.0104,0.8676</t>
+  </si>
+  <si>
+    <t>0.0010,0.0034,0.0009,0.9983</t>
+  </si>
+  <si>
+    <t>0.0006,0.0028,0.0006,0.9990</t>
+  </si>
+  <si>
+    <t>0.0200,0.0008,0.0012,0.9914</t>
+  </si>
+  <si>
+    <t>0.0064,0.8724,0.3229,0.0021</t>
+  </si>
+  <si>
+    <t>0.9938,0.0026,0.0027,0.0008</t>
+  </si>
+  <si>
+    <t>0.2079,0.8649,0.0026,0.0024</t>
+  </si>
+  <si>
+    <t>0.9923,0.0040,0.0018,0.0014</t>
+  </si>
+  <si>
+    <t>0.3684,0.7998,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.9825,0.0072,0.0028,0.0047</t>
+  </si>
+  <si>
+    <t>0.0821,0.0026,0.0015,0.9630</t>
+  </si>
+  <si>
+    <t>0.9856,0.0064,0.0030,0.0041</t>
+  </si>
+  <si>
+    <t>0.0125,0.0082,0.9822,0.0078</t>
+  </si>
+  <si>
+    <t>0.8891,0.0036,0.0105,0.1157</t>
+  </si>
+  <si>
+    <t>0.9604,0.0118,0.0056,0.0161</t>
+  </si>
+  <si>
+    <t>0.5654,0.3260,0.1009,0.0149</t>
+  </si>
+  <si>
+    <t>0.6367,0.4050,0.0018,0.0063</t>
+  </si>
+  <si>
+    <t>0.9845,0.0154,0.0039,0.0008</t>
+  </si>
+  <si>
+    <t>0.4508,0.6585,0.0064,0.0028</t>
+  </si>
+  <si>
+    <t>0.9167,0.0530,0.0331,0.0115</t>
+  </si>
+  <si>
+    <t>0.9721,0.0281,0.0071,0.0017</t>
+  </si>
+  <si>
+    <t>0.9940,0.0043,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9957,0.0019,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9964,0.0011,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9958,0.0012,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9967,0.0011,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9840,0.0134,0.0045,0.0011</t>
+  </si>
+  <si>
+    <t>0.9936,0.0052,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9955,0.0005,0.0004,0.0018</t>
+  </si>
+  <si>
+    <t>0.9686,0.0736,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.8200,0.2340,0.0139,0.0022</t>
+  </si>
+  <si>
+    <t>0.7374,0.4031,0.0027,0.0007</t>
+  </si>
+  <si>
+    <t>0.0132,0.3463,0.9427,0.0075</t>
+  </si>
+  <si>
+    <t>0.9878,0.0103,0.0030,0.0009</t>
+  </si>
+  <si>
+    <t>0.9727,0.0221,0.0047,0.0023</t>
+  </si>
+  <si>
+    <t>0.9927,0.0056,0.0013,0.0010</t>
+  </si>
+  <si>
+    <t>0.9864,0.0094,0.0010,0.0022</t>
+  </si>
+  <si>
+    <t>0.0005,0.0275,0.9972,0.0004</t>
+  </si>
+  <si>
+    <t>0.9541,0.0536,0.0071,0.0016</t>
+  </si>
+  <si>
+    <t>0.0006,0.1079,0.9944,0.0003</t>
+  </si>
+  <si>
+    <t>0.0163,0.1684,0.9513,0.0017</t>
+  </si>
+  <si>
+    <t>0.0147,0.0149,0.9734,0.0014</t>
+  </si>
+  <si>
+    <t>0.0221,0.0852,0.9770,0.0003</t>
+  </si>
+  <si>
+    <t>0.0074,0.0370,0.9849,0.0022</t>
+  </si>
+  <si>
+    <t>0.0011,0.0043,0.9961,0.0012</t>
+  </si>
+  <si>
+    <t>0.0012,0.0204,0.9916,0.0042</t>
+  </si>
+  <si>
+    <t>0.2059,0.0246,0.8182,0.0027</t>
+  </si>
+  <si>
+    <t>0.2776,0.0287,0.6656,0.0786</t>
+  </si>
+  <si>
+    <t>0.0836,0.0674,0.8835,0.0051</t>
+  </si>
+  <si>
+    <t>0.2015,0.1585,0.6244,0.0060</t>
+  </si>
+  <si>
+    <t>0.1276,0.1043,0.7843,0.0042</t>
+  </si>
+  <si>
+    <t>0.2713,0.0358,0.7343,0.0028</t>
+  </si>
+  <si>
+    <t>0.8466,0.0392,0.1200,0.0168</t>
+  </si>
+  <si>
+    <t>0.1309,0.0267,0.8542,0.0027</t>
+  </si>
+  <si>
+    <t>0.9008,0.1796,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.9741,0.0582,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9446,0.1135,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.9778,0.0307,0.0038,0.0009</t>
+  </si>
+  <si>
+    <t>0.8613,0.2420,0.0023,0.0018</t>
+  </si>
+  <si>
+    <t>0.8446,0.0615,0.0743,0.0055</t>
+  </si>
+  <si>
+    <t>0.9886,0.0009,0.0167,0.0003</t>
+  </si>
+  <si>
+    <t>0.8785,0.0254,0.0574,0.0184</t>
+  </si>
+  <si>
+    <t>0.7951,0.0089,0.2932,0.0033</t>
+  </si>
+  <si>
+    <t>0.7768,0.0078,0.0773,0.1042</t>
+  </si>
+  <si>
+    <t>0.0182,0.0022,0.9780,0.0024</t>
+  </si>
+  <si>
+    <t>0.0442,0.7182,0.6857,0.0163</t>
+  </si>
+  <si>
+    <t>0.0790,0.4153,0.8425,0.0183</t>
+  </si>
+  <si>
+    <t>0.2507,0.0070,0.8304,0.0013</t>
+  </si>
+  <si>
+    <t>0.0080,0.1040,0.9311,0.0051</t>
+  </si>
+  <si>
+    <t>0.9888,0.0082,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.9982,0.0006,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9924,0.0095,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9935,0.0048,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.9903,0.0090,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9923,0.0074,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9943,0.0050,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9968,0.0016,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.0075,0.0730,0.9727,0.0161</t>
+  </si>
+  <si>
+    <t>0.0381,0.7233,0.3459,0.0102</t>
+  </si>
+  <si>
+    <t>0.8639,0.0740,0.0685,0.0102</t>
+  </si>
+  <si>
+    <t>0.0037,0.0053,0.9948,0.0003</t>
+  </si>
+  <si>
+    <t>0.0040,0.2170,0.9624,0.0088</t>
+  </si>
+  <si>
+    <t>0.0059,0.3264,0.9646,0.0028</t>
+  </si>
+  <si>
+    <t>0.0210,0.0346,0.9830,0.0003</t>
+  </si>
+  <si>
+    <t>0.0649,0.0250,0.9193,0.0025</t>
+  </si>
+  <si>
+    <t>0.0015,0.0059,0.9980,0.0002</t>
+  </si>
+  <si>
+    <t>0.0288,0.0206,0.9572,0.0087</t>
+  </si>
+  <si>
+    <t>0.1810,0.2683,0.5687,0.0065</t>
+  </si>
+  <si>
+    <t>0.9030,0.0061,0.1152,0.0072</t>
+  </si>
+  <si>
+    <t>0.9040,0.0005,0.2770,0.0003</t>
+  </si>
+  <si>
+    <t>0.9341,0.0140,0.0408,0.0134</t>
+  </si>
+  <si>
+    <t>0.9972,0.0018,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9986,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0011,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9968,0.0015,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9978,0.0008,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9950,0.0060,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0013,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9985,0.0006,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0336,0.2440,0.7941,0.0019</t>
+  </si>
+  <si>
+    <t>0.0027,0.0852,0.9760,0.0008</t>
+  </si>
+  <si>
+    <t>0.0207,0.0300,0.9723,0.0012</t>
+  </si>
+  <si>
+    <t>0.0126,0.0699,0.9378,0.0061</t>
+  </si>
+  <si>
+    <t>0.1025,0.0027,0.9575,0.0011</t>
+  </si>
+  <si>
+    <t>0.1347,0.0307,0.7271,0.1716</t>
+  </si>
+  <si>
+    <t>0.2825,0.0494,0.7352,0.0088</t>
+  </si>
+  <si>
+    <t>0.0822,0.0425,0.8683,0.0394</t>
+  </si>
+  <si>
+    <t>0.7976,0.0001,0.0017,0.2664</t>
+  </si>
+  <si>
+    <t>0.1999,0.0197,0.0087,0.8774</t>
+  </si>
+  <si>
+    <t>0.2419,0.0060,0.0074,0.8698</t>
+  </si>
+  <si>
+    <t>0.0056,0.0001,0.0005,0.9974</t>
+  </si>
+  <si>
+    <t>0.0057,0.0001,0.0004,0.9979</t>
+  </si>
+  <si>
+    <t>0.9159,0.0164,0.0229,0.0548</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2387,7 +2387,7 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
         <v>295</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2625,7 +2625,7 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
         <v>312</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2681,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
         <v>316</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2863,7 +2863,7 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D67" t="s">
         <v>329</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3395,7 +3395,7 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D105" t="s">
         <v>367</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3927,7 +3927,7 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
         <v>405</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4375,7 +4375,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
         <v>437</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5075,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
         <v>487</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
